--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
@@ -47,7 +47,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8EEF5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,9 +101,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1521,21 +1513,25 @@
       <c r="F19" s="4" t="n">
         <v>770427406</v>
       </c>
-      <c r="G19" s="7" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 70</t>
+          <t>General Secondary School No. 70, Yakkabog District</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №70</t>
+          <t>Общеобразовательная школа №70 Яккабагского района</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,37 +27,15 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -86,22 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,2060 +435,1880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A3:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16.5" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="3.14" customWidth="1" min="1" max="1"/>
+    <col width="34.43" customWidth="1" min="2" max="2"/>
+    <col width="17.29" customWidth="1" min="3" max="3"/>
+    <col width="13.43" customWidth="1" min="4" max="4"/>
+    <col width="17.86" customWidth="1" min="5" max="5"/>
+    <col width="22.57" customWidth="1" min="6" max="6"/>
+    <col width="21.71" customWidth="1" min="7" max="7"/>
+    <col width="17.71" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="26.29" customWidth="1" min="10" max="10"/>
+    <col width="13.86" customWidth="1" min="11" max="11"/>
+    <col width="16.43" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Guruh 26-04 (32 nafar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Namuna: Saydalimov Anvarjon Sarvarjon o`g`li | 517******0016 | AC1686958 | 990201527 | Qashqadaryo, Qarshi | 4-mittituman 21/23 | Qarshi shahar 1-maktab | Qarshi City School No. 1 | Школа №1 города Карши | Maktab | AA1775603 | 2008-2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="63" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="47.25" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Avval o`qigan muassasa nomi(Rus tilida)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>A'zamov Shohjaxon Sherali o'g'li</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>52510085590064</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>AD9855395</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="2" t="n">
         <v>991312508</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="2" t="n">
         <v>880068282</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 9-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 9, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №9 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>UM 03728296</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Abdixalilova Shohzoda Bahodir qizi</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>60603085720124</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>AD7053449</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>930190686</v>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 96-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 96, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №96 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>UM 03719793</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Abdiyeva Sabina G'ayrat qizi</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>60108085590051</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>AE4860201</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="2" t="n">
         <v>919483879</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="2" t="n">
         <v>885967179</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 13-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 13, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №13 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>UM 03752332</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Abduraxmonova Zahrobonu Toxir qizi</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>61805095590028</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>AE4193791</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>875910918</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="2" t="n">
         <v>885660802</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 2-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 2, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №2 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>UM 03751558</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Eshpulatova Shahnoza Sherali qizi</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>61405085590065</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>AE1541155</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="2" t="n">
         <v>906752661</v>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 14, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №14 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>UM 03752459</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Eshquvatova Yulduz Asliddin qizi</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>40511985730032</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>AB5879899</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>991863023</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="2" t="n">
         <v>952282462</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Pedagogy and Tourism</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский профессиональный колледж педагогики и туризма</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>K 4603559</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2014-2017</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>G'aniyeva Asila G'ani qizi</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>41011925590038</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>AE5575300</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="2" t="n">
         <v>991534838</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="2" t="n">
         <v>700342244</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Academic Lyceum under the Tashkent Institute of Irrigation and Melioration</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Академический лицей при Ташкентском институте ирригации и мелиорации</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Litsey</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>L 125287</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2008-2011</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Halimova Sevinch Ravshan qizi</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>60908085680060</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AD8735102</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>975890062</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="2" t="n">
         <v>919561093</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 1, Kitob District</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №1 Китабского района</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>UM 03273019</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Hamroqulova Marjona O'ktam qizi</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>61104085680018</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>AE1525748</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="2" t="n">
         <v>910054908</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="2" t="n">
         <v>935533351</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 61, Kitob District</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №61 Китабского района</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>UM 03729782</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Isomiddinova Ruhshona Shavkat qizi</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>63006085680064</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>AD7684354</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="2" t="n">
         <v>995264709</v>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 5, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №5 Китабского района</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>UM 03728181</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Jalolov Javlonbek G'ani o'g'li</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>53005095680054</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>AE4994200</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №4 Китабского района</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>UM 03727965</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Karimova Shaxina Fayzulla qizi</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>61511017890023</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>AC0413538</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>904403666</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="2" t="n">
         <v>912204218</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz yengil sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Light Industry and Services</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский профессиональный колледж лёгкой промышленности и сервиса</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>D 009611</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Mahmudova Gulsanam Nigmatovna</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>62308085680109</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>AE1695093</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="2" t="n">
         <v>880306601</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="2" t="n">
         <v>970874905</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 51-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 51, Kitob District</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №51 Китабского района</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>UM 03729493</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Maxmudova Musallam Qamariddin qizi</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>61303085680079</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>AE5297116</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>505899948</v>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Kitob District</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №23 Китабского района</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>UM 03728687</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Murodova Ruhshona Ilhomovna</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>61009085680098</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>AE3287114</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="2" t="n">
         <v>900709579</v>
       </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Kitob District</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №6 Китабского района</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>UM 03728240</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Nafasova Sevinch Bollijon qizi</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>62708085730015</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>AE4668322</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>991682082</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="2" t="n">
         <v>770427406</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Yakkabog District</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №70 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>UM 03758021</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Pirnazarova Jasmina Olim qizi</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>60506085680077</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>AE4198928</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="2" t="n">
         <v>908841208</v>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 32, Kitob District</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №32 Китабского района</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>UM 03729001</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>60203045680015</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>AC2359638</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>888270718</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="2" t="n">
         <v>883860485</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 18-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 18, Kitob District</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №18 Китабского района</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>DB 00173015</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>2010-2021</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Soyipova Dinora Sanjar qizi</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>62208085590065</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>AD9484395</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 22-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 22, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №22 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>UM 03297405</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>60108085590037</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>AD9863476</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="2" t="n">
         <v>908780280</v>
       </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 56-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 56, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №56 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>UM 03755218</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>60112075590084</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>AD6024952</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>883367774</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="2" t="n">
         <v>907163142</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 14, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №14 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>UM 03296212</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>60508095680049</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>AE4114421</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="2" t="n">
         <v>975732292</v>
       </c>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 34-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 34, Kitob District</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №34 Китабского района</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>UM-O 00064269</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Ulugbekova Zara Ulug'bek qizi</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>61109085590127</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>AE4760779</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>882633833</v>
       </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 5, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №5 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>UM 03728161</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="4" t="n">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>62701015680026</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>AB8517012</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>885872701</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="2" t="n">
         <v>910704107</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Kitob qishloq xo'jalik kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Kitob Agricultural Vocational College</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Китабский сельскохозяйственный профессиональный колледж</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>K 5487959</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>60206045680052</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>AD0284895</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="2" t="n">
         <v>871160303</v>
       </c>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Specialized School No. 1 with In-Depth Study of Certain Subjects, Kitob District</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Специализированная школа №1 с углублённым изучением отдельных предметов Китабского района</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>UM 0862565</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2010-2021</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="4" t="n">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>62104025680040</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>AD4186543</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>883851378</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="2" t="n">
         <v>884188278</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 63-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 63, Kitob District</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №63 Китабского района</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>UM 0086260</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>2008-2019</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="4" t="n">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>60110085590193</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>AE1516812</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="2" t="n">
         <v>879340301</v>
       </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 60, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №60 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>UM 03755333</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="4" t="n">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>62204085720105</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>AE5954513</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="2" t="n">
         <v>976760905</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="2" t="n">
         <v>876317371</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 19, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №19 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>UM 03717652</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="n">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>60411015680031</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>AC1847101</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>333801121</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="2" t="n">
         <v>880096166</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 3, Kitob District</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №3 Китабского района</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>UM 0084478</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2008-2019</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="n">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>63004075680030</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>AD4921163</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>701202277</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="2" t="n">
         <v>880096166</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 3, Kitob District</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №3 Китабского района</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>UM 02149677</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="n">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>60110085590092</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>AE5015467</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="2" t="n">
         <v>887291401</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="2" t="n">
         <v>976198484</v>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №15 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>UM 03753649</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="4" t="n">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>63112085680039</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>AE5856503</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="2" t="n">
         <v>908785105</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="2" t="n">
         <v>916397685</v>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 53-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 53, Kitob District</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №53 Китабского района</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>UM 03729571</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
@@ -435,22 +435,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:M35"/>
+  <dimension ref="A3:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.14" customWidth="1" min="1" max="1"/>
-    <col width="34.43" customWidth="1" min="2" max="2"/>
-    <col width="17.29" customWidth="1" min="3" max="3"/>
-    <col width="13.43" customWidth="1" min="4" max="4"/>
-    <col width="17.86" customWidth="1" min="5" max="5"/>
-    <col width="22.57" customWidth="1" min="6" max="6"/>
-    <col width="21.71" customWidth="1" min="7" max="7"/>
-    <col width="17.71" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="26.29" customWidth="1" min="10" max="10"/>
-    <col width="13.86" customWidth="1" min="11" max="11"/>
-    <col width="16.43" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34.43" customWidth="1" min="3" max="3"/>
+    <col width="17.29" customWidth="1" min="4" max="4"/>
+    <col width="13.43" customWidth="1" min="5" max="5"/>
+    <col width="17.86" customWidth="1" min="6" max="6"/>
+    <col width="22.57" customWidth="1" min="7" max="7"/>
+    <col width="21.71" customWidth="1" min="8" max="8"/>
+    <col width="17.71" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="26.29" customWidth="1" min="11" max="11"/>
+    <col width="13.86" customWidth="1" min="12" max="12"/>
+    <col width="16.43" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="3" ht="47.25" customHeight="1">
@@ -461,60 +462,65 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>Guruhi</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
@@ -526,52 +532,57 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>A'zamov Shohjaxon Sherali o'g'li</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>52510085590064</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AD9855395</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>991312508</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>880068282</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 9-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 9, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>UM 03728296</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -583,50 +594,55 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>Abdixalilova Shohzoda Bahodir qizi</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>60603085720124</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>AD7053449</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>930190686</v>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 96-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 96, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>UM 03719793</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -638,52 +654,57 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>Abdiyeva Sabina G'ayrat qizi</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>60108085590051</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AE4860201</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>919483879</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>885967179</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 13-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 13, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>UM 03752332</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -695,52 +716,57 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>Abduraxmonova Zahrobonu Toxir qizi</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>61805095590028</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>AE4193791</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>875910918</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>885660802</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 2-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 2, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>UM 03751558</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -752,50 +778,55 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>Eshpulatova Shahnoza Sherali qizi</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>61405085590065</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AE1541155</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>906752661</v>
       </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 14, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>UM 03752459</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -807,52 +838,57 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Eshquvatova Yulduz Asliddin qizi</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>40511985730032</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AB5879899</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>991863023</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>952282462</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Pedagogy and Tourism</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>K 4603559</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2014-2017</t>
         </is>
@@ -864,52 +900,57 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>G'aniyeva Asila G'ani qizi</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>41011925590038</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AE5575300</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>991534838</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>700342244</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Academic Lyceum under the Tashkent Institute of Irrigation and Melioration</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Litsey</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>L 125287</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2008-2011</t>
         </is>
@@ -921,52 +962,57 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Halimova Sevinch Ravshan qizi</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>60908085680060</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>AD8735102</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>975890062</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>919561093</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 1, Kitob District</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>UM 03273019</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -978,52 +1024,57 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Hamroqulova Marjona O'ktam qizi</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>61104085680018</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AE1525748</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>910054908</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>935533351</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 61, Kitob District</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>UM 03729782</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1035,50 +1086,55 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>Isomiddinova Ruhshona Shavkat qizi</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>63006085680064</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>AD7684354</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>995264709</v>
       </c>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 5, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>UM 03728181</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1090,48 +1146,53 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Jalolov Javlonbek G'ani o'g'li</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>53005095680054</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>AE4994200</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>UM 03727965</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1143,52 +1204,57 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>Karimova Shaxina Fayzulla qizi</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>61511017890023</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>AC0413538</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>904403666</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>912204218</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz yengil sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Light Industry and Services</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>D 009611</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1200,52 +1266,57 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>Mahmudova Gulsanam Nigmatovna</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>62308085680109</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AE1695093</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>880306601</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>970874905</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 51-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 51, Kitob District</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>UM 03729493</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1257,50 +1328,55 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>Maxmudova Musallam Qamariddin qizi</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>61303085680079</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>AE5297116</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>505899948</v>
       </c>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Kitob District</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>UM 03728687</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1312,50 +1388,55 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Murodova Ruhshona Ilhomovna</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>61009085680098</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AE3287114</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" s="2" t="n">
         <v>900709579</v>
       </c>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Kitob District</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>UM 03728240</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1367,52 +1448,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>Nafasova Sevinch Bollijon qizi</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>62708085730015</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>AE4668322</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>991682082</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>770427406</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Yakkabog District</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>UM 03758021</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1424,50 +1510,55 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Pirnazarova Jasmina Olim qizi</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>60506085680077</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>AE4198928</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>908841208</v>
       </c>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 32, Kitob District</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>UM 03729001</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1479,52 +1570,57 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>60203045680015</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>AC2359638</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>888270718</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>883860485</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 18-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 18, Kitob District</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>DB 00173015</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>2010-2021</t>
         </is>
@@ -1536,48 +1632,53 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>Soyipova Dinora Sanjar qizi</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>62208085590065</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AD9484395</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 22-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 22, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>UM 03297405</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -1589,50 +1690,55 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>60108085590037</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>AD9863476</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>908780280</v>
       </c>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 56-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 56, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>UM 03755218</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1644,52 +1750,57 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>60112075590084</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AD6024952</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>883367774</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>907163142</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 14, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>UM 03296212</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -1701,50 +1812,55 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>60508095680049</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>AE4114421</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>975732292</v>
       </c>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 34-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 34, Kitob District</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>UM-O 00064269</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1756,50 +1872,55 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>Ulugbekova Zara Ulug'bek qizi</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>61109085590127</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>AE4760779</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>882633833</v>
       </c>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 5, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>UM 03728161</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
@@ -1811,52 +1932,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>62701015680026</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>AB8517012</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>885872701</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>910704107</v>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Kitob qishloq xo'jalik kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Kitob Agricultural Vocational College</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>K 5487959</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1868,50 +1994,55 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>60206045680052</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>AD0284895</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>871160303</v>
       </c>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Specialized School No. 1 with In-Depth Study of Certain Subjects, Kitob District</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>UM 0862565</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2010-2021</t>
         </is>
@@ -1923,52 +2054,57 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>62104025680040</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>AD4186543</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>883851378</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>884188278</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 63-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 63, Kitob District</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>UM 0086260</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>2008-2019</t>
         </is>
@@ -1980,50 +2116,55 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>60110085590193</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>AE1516812</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>879340301</v>
       </c>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 60, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>UM 03755333</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2035,52 +2176,57 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>62204085720105</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>AE5954513</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>976760905</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>876317371</v>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 19, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
           <t>UM 03717652</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
@@ -2092,52 +2238,57 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>60411015680031</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>AC1847101</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" s="2" t="n">
         <v>333801121</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>880096166</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 3, Kitob District</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t>UM 0084478</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>2008-2019</t>
         </is>
@@ -2149,52 +2300,57 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>63004075680030</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>AD4921163</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" s="2" t="n">
         <v>701202277</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>880096166</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 3, Kitob District</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>UM 02149677</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
@@ -2206,52 +2362,57 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>60110085590092</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>AE5015467</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>887291401</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>976198484</v>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>UM 03753649</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2263,52 +2424,57 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>63112085680039</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>AE5856503</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>908785105</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>916397685</v>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 53-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 53, Kitob District</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
           <t>UM 03729571</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
@@ -551,17 +551,21 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>991312508</v>
+        <v>913125080</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>880068282</v>
+        <v>760782870</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Kichik novqat mfy, Soyboʻyi koʻchasi, 04</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 9-sonli umumiy o'rta ta'lim maktabi</t>
@@ -613,15 +617,21 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>930190686</v>
-      </c>
-      <c r="G5" s="2" t="n"/>
+        <v>33187080</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>11906860</v>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Quruq soy MFY, Buzovut qishlogʻi, 111-uy</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 96-sonli umumiy o'rta ta'lim maktabi</t>
@@ -735,17 +745,21 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>875910918</v>
+        <v>759109180</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>885660802</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Uymovut MFY, Qadriyat ko'chasi, 127-uy</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 2-sonli umumiy o'rta ta'lim maktabi</t>
@@ -797,15 +811,21 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>906752661</v>
-      </c>
-      <c r="G8" s="2" t="n"/>
+        <v>763104770</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>732104770</v>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Bunyodkor, Sadriddin ayni, 6_uy</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
@@ -860,14 +880,18 @@
         <v>991863023</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>952282462</v>
+        <v>991863023</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n"/>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Alakuylak MFY, Hamid Olimjon koʻchasi, 55.0</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
@@ -991,7 +1015,11 @@
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Hamid Olimjon, Hamid Olimjon 213, 213uy</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1105,15 +1133,21 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>995264709</v>
-      </c>
-      <c r="G13" s="2" t="n"/>
+        <v>834030080</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>952647090</v>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Guliston MFY, Qoʻshtepa kòchasi, 329.0</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1164,14 +1198,22 @@
           <t>AE4994200</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>1114090</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>973891174</v>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Charimgar MFY, Navoiy kucha, 44uy</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1223,17 +1265,21 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>904403666</v>
+        <v>44036660</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>912204218</v>
+        <v>122477210</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Fayzobod MFY, Yangi kesh, 242-uy</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz yengil sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
@@ -1285,17 +1331,21 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>880306601</v>
+        <v>884943800</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>970874905</v>
+        <v>880449802</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Iskana MFY, Uchtepalik, 52.0</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 51-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1347,15 +1397,21 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>505899948</v>
-      </c>
-      <c r="G17" s="2" t="n"/>
+        <v>58999480</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>73473860</v>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Sho'robsoy MFY, Komillik ko'chasi, 18uy</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1407,15 +1463,21 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>900709579</v>
-      </c>
-      <c r="G18" s="2" t="n"/>
+        <v>874637908</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>107095790</v>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Beshqazoq MFY, Oq daryo, 56-uy</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1467,17 +1529,21 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>991682082</v>
+        <v>916820820</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>770427406</v>
+        <v>916820820</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Qoʻshchinor, AbulqosimFirdavsiy, 22-uy</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1529,15 +1595,21 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>908841208</v>
-      </c>
-      <c r="G20" s="2" t="n"/>
+        <v>88412080</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>195727170</v>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49.0</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1589,17 +1661,21 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>888270718</v>
+        <v>883879404</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>883860485</v>
+        <v>883813979</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Yakatut MFY, Kumirtepa kuchasi, 60uy</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 18-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1709,15 +1785,21 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>908780280</v>
-      </c>
-      <c r="G23" s="2" t="n"/>
+        <v>87802800</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>526948780</v>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Xitoy MFY, Besh chinor, 65.0</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 56-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1769,17 +1851,21 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>883367774</v>
+        <v>833677740</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>907163142</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Do'stlik MFY, Bunyodkor ko'chasi, 62/16-uy</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1891,15 +1977,21 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
+        <v>702902740</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>882633833</v>
       </c>
-      <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Guliston MFY, Qo'shtepa mahallasi, 75.0</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1951,17 +2043,21 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>885872701</v>
+        <v>858727010</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>910704107</v>
+        <v>68720885</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Hoʻjailimkoni MFY, Hoʻjailimkoni qishlogʻi, 248-uy</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Kitob qishloq xo'jalik kasb-hunar kolleji</t>
@@ -2013,15 +2109,21 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>871160303</v>
-      </c>
-      <c r="G28" s="2" t="n"/>
+        <v>711603030</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>711603030</v>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Homid Olimjom MFY, Amir Temur kochasi, 47 uy</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
@@ -2083,7 +2185,11 @@
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Obikanda MFY, Baland Tepa koʻchasi, 23-uy</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 63-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2135,15 +2241,21 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>879340301</v>
-      </c>
-      <c r="G30" s="2" t="n"/>
+        <v>793403010</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>872288840</v>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Xonabod MFY, Samarqand kuchasi, 85-uy</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 60-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2319,17 +2431,21 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>701202277</v>
+        <v>68161770</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>880096166</v>
+        <v>961660883</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Xalqlar do'stligi MFY, Qashqadaryo2, 65.0</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 3-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2443,17 +2559,21 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>908785105</v>
+        <v>311580830</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>916397685</v>
+        <v>883800339</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Bogʻibaland MFY, Xirmanjoy kòchasi, 121-uy</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 53-sonli umumiy o'rta ta'lim maktabi</t>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-04).xlsx
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>913125080</v>
+        <v>991312508</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>760782870</v>
+        <v>886078287</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Kichik novqat mfy, Soyboʻyi koʻchasi, 04</t>
+          <t>Maktobod mfy, Soyboʻyi koʻchasi, 4-uy</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>33187080</v>
+        <v>703318708</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>11906860</v>
+        <v>701190686</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Quruq soy MFY, Buzovut qishlogʻi, 111-uy</t>
+          <t>Quruqsoy MFY, Buzovut qishlogʻi, 111-uy</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -683,17 +683,21 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
+        <v>879266108</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>919483879</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>885967179</v>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Nomozgoh MFY, Taragʻay Bahodir, 2.31-uy</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 13-sonli umumiy o'rta ta'lim maktabi</t>
@@ -745,14 +749,14 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>759109180</v>
+        <v>875910918</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>885660802</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shaxrisabz shahri</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -811,14 +815,14 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>763104770</v>
+        <v>876310477</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>732104770</v>
+        <v>873210477</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,12 +888,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Yakkabogʻ tumani</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Alakuylak MFY, Hamid Olimjon koʻchasi, 55.0</t>
+          <t>Alakuylak MFY, Hamid Olimjon koʻchasi, 55-uy</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1071,17 +1075,21 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>910054908</v>
+        <v>882054908</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>935533351</v>
+        <v>887533351</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Katlos MFY, Bogʻiston kòchasi, 28-uy</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1133,19 +1141,19 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>834030080</v>
+        <v>883403008</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>952647090</v>
+        <v>995264709</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Guliston MFY, Qoʻshtepa kòchasi, 329.0</t>
+          <t>Guliston MFY, Qoʻshtepa kòchasi, 329-uy</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1199,7 +1207,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1114090</v>
+        <v>500111409</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>973891174</v>
@@ -1265,10 +1273,10 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>44036660</v>
+        <v>904403666</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>122477210</v>
+        <v>912247721</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1343,7 +1351,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Iskana MFY, Uchtepalik, 52.0</t>
+          <t>Iskana MFY, Uchtepalik, 52-uy</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1397,14 +1405,14 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>58999480</v>
+        <v>505899948</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>73473860</v>
+        <v>507347386</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
+          <t>Qashqadaryo, Boshchil qishlog'i</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1466,7 +1474,7 @@
         <v>874637908</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>107095790</v>
+        <v>910709579</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1529,14 +1537,14 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>916820820</v>
+        <v>991682082</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>916820820</v>
+        <v>991682082</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Yakkabogʻ tumani</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1595,10 +1603,10 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>88412080</v>
+        <v>908841208</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>195727170</v>
+        <v>919572717</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1615,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49.0</t>
+          <t>Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49-uy</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1726,14 +1734,22 @@
           <t>AD9484395</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="F22" s="2" t="n">
+        <v>938041814</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>973858369</v>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Abziyat MFY, Hidoyat ko’chasi, 1-uy</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 22-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1785,19 +1801,19 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>87802800</v>
+        <v>908780280</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>526948780</v>
+        <v>952694878</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tuman</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Xitoy MFY, Besh chinor, 65.0</t>
+          <t>Xitoy MFY, Besh chinor, 65-uy</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1851,14 +1867,14 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>833677740</v>
+        <v>883367774</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>907163142</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1977,7 +1993,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>702902740</v>
+        <v>770290274</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>882633833</v>
@@ -1989,7 +2005,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Guliston MFY, Qo'shtepa mahallasi, 75.0</t>
+          <t>Guliston MFY, Qo'shtepa mahallasi, 75-uy</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2043,10 +2059,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>858727010</v>
+        <v>885872701</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>68720885</v>
+        <v>884906872</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2109,10 +2125,10 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>711603030</v>
+        <v>871160303</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>711603030</v>
+        <v>871160303</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2241,14 +2257,14 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>793403010</v>
+        <v>879340301</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>872288840</v>
+        <v>887228884</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2307,17 +2323,21 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>976760905</v>
+        <v>977874795</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>876317371</v>
+        <v>976979592</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Chiroqchi MFY, Elabot kuchasi, 227-uy</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 19-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2372,14 +2392,18 @@
         <v>333801121</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>880096166</v>
+        <v>935629405</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Nurali MFY, Nurali qishlogi, 75-uy</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 3-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2431,10 +2455,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>68161770</v>
+        <v>706816177</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>961660883</v>
+        <v>880096166</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2443,7 +2467,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Xalqlar do'stligi MFY, Qashqadaryo2, 65.0</t>
+          <t>Xalqlar do'stligi MFY, Qashqadaryo2, 65-uy</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2500,14 +2524,18 @@
         <v>887291401</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>976198484</v>
+        <v>973878737</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Qumqishloq MFY, Hoji koʻchasi, 2-uy</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2559,10 +2587,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>311580830</v>
+        <v>331158083</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>883800339</v>
+        <v>976188380</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
